--- a/NECP Scenario/Results/Regional Results/CHIOS_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/CHIOS_Generation.xlsx
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.911132455975764E-08</v>
+        <v>5.770271544559797E-08</v>
       </c>
       <c r="C3">
-        <v>2.271729594352716E-08</v>
+        <v>3.351039779293079E-08</v>
       </c>
       <c r="D3">
-        <v>0.06623472128647025</v>
+        <v>0.06578015136626109</v>
       </c>
       <c r="E3">
-        <v>0.06684370589892667</v>
+        <v>0.06472108354345736</v>
       </c>
       <c r="F3">
-        <v>0.06886448530620511</v>
+        <v>0.0667042651964234</v>
       </c>
       <c r="G3">
-        <v>0.001269458824145178</v>
+        <v>0.004311626033280662</v>
       </c>
       <c r="H3">
-        <v>0.001276866230278798</v>
+        <v>0.004778339524485504</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.324462587801585E-08</v>
+        <v>4.904730813055831E-08</v>
       </c>
       <c r="C4">
-        <v>1.930970155421992E-08</v>
+        <v>2.848383812579123E-08</v>
       </c>
       <c r="D4">
-        <v>0.05629951309357802</v>
+        <v>0.05591312866131919</v>
       </c>
       <c r="E4">
-        <v>0.05681715001410391</v>
+        <v>0.05501292101193807</v>
       </c>
       <c r="F4">
-        <v>0.05853481251027345</v>
+        <v>0.05669862541695986</v>
       </c>
       <c r="G4">
-        <v>0.001079040000523398</v>
+        <v>0.003664882128288572</v>
       </c>
       <c r="H4">
-        <v>0.001085336295736991</v>
+        <v>0.004061588595812687</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.1703234007868139</v>
+        <v>0.1703234021724123</v>
       </c>
       <c r="C14">
-        <v>0.1939026836355208</v>
+        <v>0.1939026842481059</v>
       </c>
       <c r="D14">
-        <v>0.2140663522771582</v>
+        <v>0.2140663423020016</v>
       </c>
       <c r="E14">
-        <v>0.2573263265823896</v>
+        <v>0.2573247285901546</v>
       </c>
       <c r="F14">
-        <v>0.2647736830881685</v>
+        <v>0.2586454242648805</v>
       </c>
       <c r="G14">
-        <v>0.2979969021066771</v>
+        <v>0.2979969406173116</v>
       </c>
       <c r="H14">
-        <v>0.3928200441641134</v>
+        <v>0.3928202777036367</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1213,25 +1213,25 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0.3909604634376805</v>
+        <v>0.3909604861934894</v>
       </c>
       <c r="C28">
-        <v>0.4564049835697067</v>
+        <v>0.456404994636222</v>
       </c>
       <c r="D28">
-        <v>0.1306672726931</v>
+        <v>0.1285761095849599</v>
       </c>
       <c r="E28">
-        <v>4.588839943329608E-08</v>
+        <v>6.824408323045151E-08</v>
       </c>
       <c r="F28">
-        <v>4.431086183568548E-08</v>
+        <v>6.565856534209541E-08</v>
       </c>
       <c r="G28">
-        <v>0.000892362820021529</v>
+        <v>0.000835071710891974</v>
       </c>
       <c r="H28">
-        <v>0.001673174162557123</v>
+        <v>0.0013856808115971</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1239,25 +1239,25 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.1437354644863905</v>
+        <v>0.1437354728464123</v>
       </c>
       <c r="C29">
-        <v>0.1677959498351352</v>
+        <v>0.1677959539005194</v>
       </c>
       <c r="D29">
-        <v>0.04803943848030004</v>
+        <v>0.04727062850938611</v>
       </c>
       <c r="E29">
-        <v>1.685630337388523E-08</v>
+        <v>2.506842489029598E-08</v>
       </c>
       <c r="F29">
-        <v>1.626953889090645E-08</v>
+        <v>2.410784659154254E-08</v>
       </c>
       <c r="G29">
-        <v>0.0003280745349869318</v>
+        <v>0.0003070116123539982</v>
       </c>
       <c r="H29">
-        <v>0.0006151373705436098</v>
+        <v>0.0005094411955335807</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1271,19 +1271,19 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0.1155657212842747</v>
+        <v>0.1138259256404696</v>
       </c>
       <c r="E30">
-        <v>0.2046233119976911</v>
+        <v>0.1912143739011458</v>
       </c>
       <c r="F30">
-        <v>0.2258110134748102</v>
+        <v>0.2081451815236691</v>
       </c>
       <c r="G30">
-        <v>0.2240569542178293</v>
+        <v>0.2065866100806248</v>
       </c>
       <c r="H30">
-        <v>0.229379651651278</v>
+        <v>0.2133803978669699</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.007867200041943509</v>
+        <v>0.007867198579514702</v>
       </c>
       <c r="C31">
-        <v>0.0078672017654939</v>
+        <v>0.007867201124998622</v>
       </c>
       <c r="D31">
-        <v>0.006069745931427518</v>
+        <v>0.006078943123228071</v>
       </c>
       <c r="E31">
-        <v>0.007811455756713524</v>
+        <v>0.007758415440474065</v>
       </c>
       <c r="F31">
-        <v>0.007563062701559088</v>
+        <v>0.007568698537983319</v>
       </c>
       <c r="G31">
-        <v>0.007262300672408062</v>
+        <v>0.007275190647819846</v>
       </c>
       <c r="H31">
-        <v>0.007145626290140834</v>
+        <v>0.007122704250698663</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1323,19 +1323,19 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>4.617388823645301E-08</v>
+        <v>6.837577445343397E-08</v>
       </c>
       <c r="E32">
-        <v>3.485467596756626E-07</v>
+        <v>1.954468303472902E-06</v>
       </c>
       <c r="F32">
-        <v>0.04865579383738041</v>
+        <v>0.05492451301756747</v>
       </c>
       <c r="G32">
-        <v>0.07554484438033773</v>
+        <v>0.07554484592549826</v>
       </c>
       <c r="H32">
-        <v>0.07641647619023553</v>
+        <v>0.07641641900343819</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.0106671332591851</v>
+        <v>0.01066713189006521</v>
       </c>
       <c r="C33">
-        <v>0.01066713486291035</v>
+        <v>0.01066713425899393</v>
       </c>
       <c r="D33">
-        <v>0.01066711169583255</v>
+        <v>0.01066709948179546</v>
       </c>
       <c r="E33">
-        <v>0.01066711928082205</v>
+        <v>0.01066711137016694</v>
       </c>
       <c r="F33">
-        <v>0.01065604221605339</v>
+        <v>0.01051558188657485</v>
       </c>
       <c r="G33">
-        <v>0.01030162256676138</v>
+        <v>0.01030158255124571</v>
       </c>
       <c r="H33">
-        <v>0.01065934474179178</v>
+        <v>0.01065916863313514</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1427,19 +1427,19 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0.043455839138572</v>
+        <v>0.04606869396144426</v>
       </c>
       <c r="E36">
-        <v>0.05586101986189592</v>
+        <v>0.0592685777283148</v>
       </c>
       <c r="F36">
-        <v>0.05564045895096047</v>
+        <v>0.05912501224524559</v>
       </c>
       <c r="G36">
-        <v>0.05518359099278723</v>
+        <v>0.05895830810565089</v>
       </c>
       <c r="H36">
-        <v>0.05478179566806299</v>
+        <v>0.05801980690175142</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.02219672993088205</v>
+        <v>0.02219672725234824</v>
       </c>
       <c r="C37">
-        <v>0.02219673308569249</v>
+        <v>0.02219673191353574</v>
       </c>
       <c r="D37">
-        <v>0.01523951672902442</v>
+        <v>0.01505787467507863</v>
       </c>
       <c r="E37">
-        <v>0.02014544527883644</v>
+        <v>0.01991649819663256</v>
       </c>
       <c r="F37">
-        <v>0.01999132030444119</v>
+        <v>0.01984878352159708</v>
       </c>
       <c r="G37">
-        <v>0.01974194292605222</v>
+        <v>0.01973328945627666</v>
       </c>
       <c r="H37">
-        <v>0.01966130759023599</v>
+        <v>0.01948243775344976</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>1.15420067948023E-08</v>
+        <v>1.705208930431809E-08</v>
       </c>
       <c r="C38">
-        <v>5.059920707621614E-09</v>
+        <v>7.476489167056509E-09</v>
       </c>
       <c r="D38">
-        <v>0.03849329913940577</v>
+        <v>0.04031616234010245</v>
       </c>
       <c r="E38">
-        <v>0.008165427036212381</v>
+        <v>0.009545098876067826</v>
       </c>
       <c r="F38">
-        <v>0.00960405946610274</v>
+        <v>0.01092667982141029</v>
       </c>
       <c r="G38">
-        <v>0.01358827409648939</v>
+        <v>0.01393988983385278</v>
       </c>
       <c r="H38">
-        <v>0.0140461966305295</v>
+        <v>0.01543995100435603</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>3.911132455975764E-08</v>
+        <v>5.770271544559797E-08</v>
       </c>
       <c r="C40">
-        <v>2.271729594352716E-08</v>
+        <v>3.351039779293079E-08</v>
       </c>
       <c r="D40">
-        <v>0.06623472128647025</v>
+        <v>0.06578015136626109</v>
       </c>
       <c r="E40">
-        <v>0.06684370589892667</v>
+        <v>0.06472108354345736</v>
       </c>
       <c r="F40">
-        <v>0.06886448530620511</v>
+        <v>0.0667042651964234</v>
       </c>
       <c r="G40">
-        <v>0.001269458824145178</v>
+        <v>0.004311626033280662</v>
       </c>
       <c r="H40">
-        <v>0.001276866230278798</v>
+        <v>0.004778339524485504</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>3.324462587801585E-08</v>
+        <v>4.904730813055831E-08</v>
       </c>
       <c r="C41">
-        <v>1.930970155421992E-08</v>
+        <v>2.848383812579123E-08</v>
       </c>
       <c r="D41">
-        <v>0.05629951309357802</v>
+        <v>0.05591312866131919</v>
       </c>
       <c r="E41">
-        <v>0.05681715001410391</v>
+        <v>0.05501292101193807</v>
       </c>
       <c r="F41">
-        <v>0.05853481251027345</v>
+        <v>0.05669862541695986</v>
       </c>
       <c r="G41">
-        <v>0.001079040000523398</v>
+        <v>0.003664882128288572</v>
       </c>
       <c r="H41">
-        <v>0.001085336295736991</v>
+        <v>0.004061588595812687</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-5.866698681741792E-09</v>
+        <v>-8.655407315039658E-09</v>
       </c>
       <c r="C42">
-        <v>-3.407594389307238E-09</v>
+        <v>-5.026559667139565E-09</v>
       </c>
       <c r="D42">
-        <v>-0.009935208192892224</v>
+        <v>-0.009867022704941893</v>
       </c>
       <c r="E42">
-        <v>-0.01002655588482276</v>
+        <v>-0.009708162531519286</v>
       </c>
       <c r="F42">
-        <v>-0.01032967279593165</v>
+        <v>-0.01000563977946354</v>
       </c>
       <c r="G42">
-        <v>-0.0001904188236217796</v>
+        <v>-0.0006467439049920899</v>
       </c>
       <c r="H42">
-        <v>-0.0001915299345418072</v>
+        <v>-0.000716750928672817</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1612,16 +1612,16 @@
         <v>-0</v>
       </c>
       <c r="E43">
-        <v>-0.01583680955972776</v>
+        <v>-0.005873474082215399</v>
       </c>
       <c r="F43">
-        <v>-0.02849897120650957</v>
+        <v>-0.0207581577612644</v>
       </c>
       <c r="G43">
-        <v>-0.002303972898325846</v>
+        <v>0.01186484496132567</v>
       </c>
       <c r="H43">
-        <v>0.08944479163622167</v>
+        <v>0.1030389817821435</v>
       </c>
     </row>
     <row r="44" spans="1:8">
